--- a/per-stock/AAOI/financials.xlsx
+++ b/per-stock/AAOI/financials.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (annual)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (quarterly)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet (annual)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (annual)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data flags" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FY Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Income stmt (annual)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Income stmt (quarterly)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Balance sheet (annual)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Balance sheet (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cash flow (annual)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cash flow (quarterly)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Data flags" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -61,11 +67,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,7 +540,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15275013120</v>
+        <v>12987292672</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -546,7 +555,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15115729920</v>
+        <v>12828008448</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -578,7 +587,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>39.891033</v>
+        <v>33.9166</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -593,7 +602,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>30.128231</v>
+        <v>25.615961</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -713,11 +722,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-445583264</v>
+        <v>-418282000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>yfinance info.freeCashflow</t>
+          <t>statement: TTM OCF - |capex| (yfinance quarterly_cashflow)</t>
         </is>
       </c>
     </row>
@@ -743,7 +752,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>190.36</v>
+        <v>161.85</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -787,6 +796,477 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fiscal-year summary (GAAP, $ except where noted)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FY-3</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FY-2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FY-1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TTM</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source / formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fiscal period end</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TTM → 2026-03-31</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>annual statement headers; TTM = Σ last 4 quarters</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>'Income stmt (annual)'!D49</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>'Income stmt (annual)'!C49</f>
+        <v/>
+      </c>
+      <c r="D3" s="3">
+        <f>'Income stmt (annual)'!B49</f>
+        <v/>
+      </c>
+      <c r="E3" s="3">
+        <f>SUM('Income stmt (quarterly)'!B48:E48)</f>
+        <v/>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>'Income stmt (annual)'!D47</f>
+        <v/>
+      </c>
+      <c r="C4" s="3">
+        <f>'Income stmt (annual)'!C47</f>
+        <v/>
+      </c>
+      <c r="D4" s="3">
+        <f>'Income stmt (annual)'!B47</f>
+        <v/>
+      </c>
+      <c r="E4" s="3">
+        <f>SUM('Income stmt (quarterly)'!B46:E46)</f>
+        <v/>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gross Profit (GAAP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
+        <f>IFERROR(B4/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C5" s="4">
+        <f>IFERROR(C4/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>IFERROR(D4/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
+        <f>IFERROR(E4/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>GAAP = gross profit / revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>'Income stmt (annual)'!D39</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>'Income stmt (annual)'!C39</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>'Income stmt (annual)'!B39</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>SUM('Income stmt (quarterly)'!B38:E38)</f>
+        <v/>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <f>IFERROR(B6/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="4">
+        <f>IFERROR(C6/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="4">
+        <f>IFERROR(D6/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="4">
+        <f>IFERROR(E6/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f> operating income / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>'Income stmt (annual)'!D10</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>'Income stmt (annual)'!C10</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>'Income stmt (annual)'!B10</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>SUM('Income stmt (quarterly)'!B10:E10)</f>
+        <v/>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Free cash flow</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>'Cash flow (annual)'!D2</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>'Cash flow (annual)'!C2</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>'Cash flow (annual)'!B2</f>
+        <v/>
+      </c>
+      <c r="E9" s="3">
+        <f>SUM('Cash flow (quarterly)'!B2:E2)</f>
+        <v/>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FCF = OCF − capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FCF margin %</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <f>IFERROR(B9/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="4">
+        <f>IFERROR(C9/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="4">
+        <f>IFERROR(D9/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="4">
+        <f>IFERROR(E9/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f> FCF / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>-'Cash flow (annual)'!D6</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>-'Cash flow (annual)'!C6</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>-'Cash flow (annual)'!B6</f>
+        <v/>
+      </c>
+      <c r="E11" s="3">
+        <f>-SUM('Cash flow (quarterly)'!B6:E6)</f>
+        <v/>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Capex (shown positive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Capex / revenue %</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <f>IFERROR(B11/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="4">
+        <f>IFERROR(C11/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="4">
+        <f>IFERROR(D11/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="4">
+        <f>IFERROR(E11/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f> capex / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Net debt</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>'Balance sheet (annual)'!D4</f>
+        <v/>
+      </c>
+      <c r="C13" s="3">
+        <f>'Balance sheet (annual)'!C4</f>
+        <v/>
+      </c>
+      <c r="D13" s="3">
+        <f>'Balance sheet (annual)'!B4</f>
+        <v/>
+      </c>
+      <c r="E13" s="3">
+        <f>'Balance sheet (quarterly)'!B4</f>
+        <v/>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Net debt; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B14" s="5">
+        <f>IFERROR(B13/B8,"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="5">
+        <f>IFERROR(C13/C8,"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>IFERROR(D13/D8,"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>IFERROR(E13/E8,"")</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f> net debt / EBITDA</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Share count (period-end, M)</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>'Balance sheet (annual)'!D2/1e6</f>
+        <v/>
+      </c>
+      <c r="C15" s="6">
+        <f>'Balance sheet (annual)'!C2/1e6</f>
+        <v/>
+      </c>
+      <c r="D15" s="6">
+        <f>'Balance sheet (annual)'!B2/1e6</f>
+        <v/>
+      </c>
+      <c r="E15" s="6">
+        <f>'Balance sheet (quarterly)'!B2/1e6</f>
+        <v/>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>shares ÷ 1e6; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Share count YoY %</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4">
+        <f>IFERROR(C15/B15-1,"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="4">
+        <f>IFERROR(D15/C15-1,"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="4">
+        <f>IFERROR(E15/D15-1,"")</f>
+        <v/>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vs prior period</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1816,13 +2296,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1832,6 +2312,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1842,30 +2323,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-06-30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-03-31</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2024-12-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-09-30</t>
         </is>
@@ -1878,10 +2364,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>-507600</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>-401940</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>0</v>
@@ -1890,9 +2376,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>-23547930</v>
+        <v>0</v>
       </c>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1901,10 +2388,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>0.21</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>0</v>
@@ -1913,9 +2400,10 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1924,21 +2412,22 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>-1871000</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>465000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>-7230000</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>-7961000</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="3" t="n">
         <v>-2777000</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>-446000</v>
-      </c>
       <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1947,21 +2436,22 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>-1269000</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>-1914000</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>-2438000</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>6081000</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="F5" s="3" t="n">
         <v>264000</v>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>-112133000</v>
-      </c>
       <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1970,21 +2460,22 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>-1269000</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>-1914000</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>-2438000</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>6081000</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F6" s="3" t="n">
         <v>264000</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>-112133000</v>
-      </c>
       <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1993,21 +2484,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>-14281000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>-2022000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>-17936000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>-9098000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>-9172000</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>-119691000</v>
-      </c>
       <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2016,21 +2508,22 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>9229000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>8205000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>7366000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>6400000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>5725000</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>5356000</v>
-      </c>
       <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2039,21 +2532,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>107228000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>92330000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>85367000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>71790000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>69315000</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>71542000</v>
-      </c>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2062,21 +2556,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>-3140000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>-1449000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>-9668000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>-1880000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>-2513000</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>-112579000</v>
-      </c>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2085,21 +2580,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>-12369000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>-9654000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>-17034000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>-8280000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>-8238000</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>-117935000</v>
-      </c>
       <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2108,21 +2604,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>874000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>-13000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>-451000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>-532000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>-710000</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>-1389000</v>
-      </c>
       <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2131,21 +2628,22 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>863000</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>844000</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>902000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>818000</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>934000</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>1754000</v>
-      </c>
       <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2154,21 +2652,22 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>1737000</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>831000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>451000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>286000</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>224000</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>365000</v>
-      </c>
       <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2177,21 +2676,22 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>-13519600</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>-509940</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>-15498000</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>-15179000</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="F15" s="3" t="n">
         <v>-9436000</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>-31105930</v>
-      </c>
       <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2200,21 +2700,22 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>-14281000</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>-2022000</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>-17936000</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="E16" s="3" t="n">
         <v>-9098000</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="F16" s="3" t="n">
         <v>-9172000</v>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>-119691000</v>
-      </c>
       <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2223,21 +2724,22 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
+        <v>164021000</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>145626000</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="D17" s="3" t="n">
         <v>133598000</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>117613000</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="F17" s="3" t="n">
         <v>108614000</v>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>106718000</v>
-      </c>
       <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2246,21 +2748,22 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
+        <v>-12991000</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>-11501000</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>-18187000</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>-15976000</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="F18" s="3" t="n">
         <v>-8937000</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>-6472000</v>
-      </c>
       <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2269,21 +2772,22 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
+        <v>75980000</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>70336000</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="D19" s="3" t="n">
         <v>63329000</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>56772000</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>50041000</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>46057000</v>
-      </c>
       <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2292,21 +2796,22 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
+        <v>75980000</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>70336000</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>63329000</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>56772000</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>50041000</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>46057000</v>
-      </c>
       <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2315,21 +2820,22 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>-0.03</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="D21" s="3" t="n">
         <v>-0.28</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>-0.16</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="F21" s="3" t="n">
         <v>-0.18</v>
       </c>
-      <c r="F21" s="3" t="n">
-        <v>-2.6</v>
-      </c>
       <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2338,21 +2844,22 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>-0.03</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>-0.28</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>-0.16</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>-0.18</v>
       </c>
-      <c r="F22" s="3" t="n">
-        <v>-2.6</v>
-      </c>
       <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2361,21 +2868,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>-14281000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>-2022000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>-17936000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>-9098000</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>-9172000</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>-119691000</v>
-      </c>
       <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2384,21 +2892,22 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>-14281000</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>-2022000</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>-17936000</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>-9098000</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="F24" s="3" t="n">
         <v>-9172000</v>
       </c>
-      <c r="F24" s="3" t="n">
-        <v>-119691000</v>
-      </c>
       <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2407,21 +2916,22 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
+        <v>-14281000</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>-2022000</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="D25" s="3" t="n">
         <v>-17936000</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="E25" s="3" t="n">
         <v>-9098000</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="F25" s="3" t="n">
         <v>-9172000</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>-119691000</v>
-      </c>
       <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2430,21 +2940,22 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
+        <v>-14281000</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>-2022000</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>-17936000</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>-9098000</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="F26" s="3" t="n">
         <v>-9172000</v>
       </c>
-      <c r="F26" s="3" t="n">
-        <v>-119691000</v>
-      </c>
       <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2453,21 +2964,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
+        <v>-14281000</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>-2022000</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>-17936000</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="E27" s="3" t="n">
         <v>-9098000</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="F27" s="3" t="n">
         <v>-9172000</v>
       </c>
-      <c r="F27" s="3" t="n">
-        <v>-119691000</v>
-      </c>
       <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2476,10 +2988,10 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
+        <v>1049000</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>-8476000</v>
-      </c>
-      <c r="C28" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>0</v>
@@ -2488,9 +3000,10 @@
         <v>0</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2499,21 +3012,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>-13232000</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>-10498000</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>-17936000</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>-9098000</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>-9172000</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>-119689000</v>
-      </c>
       <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2522,21 +3036,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
+        <v>-1229000</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>867000</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="D30" s="3" t="n">
         <v>-2517000</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="E30" s="3" t="n">
         <v>6095000</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="F30" s="3" t="n">
         <v>293000</v>
       </c>
-      <c r="F30" s="3" t="n">
-        <v>-111853000</v>
-      </c>
       <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2545,21 +3060,22 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
+        <v>40000</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>2781000</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="D31" s="3" t="n">
         <v>-79000</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>14000</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="F31" s="3" t="n">
         <v>29000</v>
       </c>
-      <c r="F31" s="3" t="n">
-        <v>280000</v>
-      </c>
       <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2567,18 +3083,21 @@
           <t>Special Income Charges</t>
         </is>
       </c>
-      <c r="B32" s="3" t="n"/>
+      <c r="B32" s="3" t="n">
+        <v>-16000</v>
+      </c>
       <c r="C32" s="3" t="n"/>
-      <c r="D32" s="3" t="n">
+      <c r="D32" s="3" t="n"/>
+      <c r="E32" s="3" t="n">
         <v>-1000</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="F32" s="3" t="n">
         <v>-8000</v>
       </c>
-      <c r="F32" s="3" t="n">
+      <c r="G32" s="3" t="n">
         <v>-112061000</v>
       </c>
-      <c r="G32" s="3" t="n">
+      <c r="H32" s="3" t="n">
         <v>-28000</v>
       </c>
     </row>
@@ -2588,18 +3107,21 @@
           <t>Gain On Sale Of Ppe</t>
         </is>
       </c>
-      <c r="B33" s="3" t="n"/>
+      <c r="B33" s="3" t="n">
+        <v>-16000</v>
+      </c>
       <c r="C33" s="3" t="n"/>
-      <c r="D33" s="3" t="n">
+      <c r="D33" s="3" t="n"/>
+      <c r="E33" s="3" t="n">
         <v>-1000</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="F33" s="3" t="n">
         <v>-8000</v>
       </c>
-      <c r="F33" s="3" t="n">
+      <c r="G33" s="3" t="n">
         <v>-99000</v>
       </c>
-      <c r="G33" s="3" t="n">
+      <c r="H33" s="3" t="n">
         <v>-28000</v>
       </c>
     </row>
@@ -2610,21 +3132,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
+        <v>-1253000</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>-1876000</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="D34" s="3" t="n">
         <v>-2438000</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="E34" s="3" t="n">
         <v>6082000</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="F34" s="3" t="n">
         <v>272000</v>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>-72000</v>
-      </c>
       <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2633,21 +3156,22 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
+        <v>874000</v>
+      </c>
+      <c r="C35" s="3" t="n">
         <v>-13000</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="D35" s="3" t="n">
         <v>-451000</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="E35" s="3" t="n">
         <v>-532000</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="F35" s="3" t="n">
         <v>-710000</v>
       </c>
-      <c r="F35" s="3" t="n">
-        <v>-1389000</v>
-      </c>
       <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2656,21 +3180,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>863000</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>844000</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>902000</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>818000</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>934000</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>1754000</v>
-      </c>
       <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2679,21 +3204,22 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>1737000</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>831000</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>451000</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>286000</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="F37" s="3" t="n">
         <v>224000</v>
       </c>
-      <c r="F37" s="3" t="n">
-        <v>365000</v>
-      </c>
       <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2702,21 +3228,22 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
+        <v>-12877000</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>-11352000</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>-14968000</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>-14661000</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="F38" s="3" t="n">
         <v>-8755000</v>
       </c>
-      <c r="F38" s="3" t="n">
-        <v>-6447000</v>
-      </c>
       <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2725,21 +3252,22 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
+        <v>56793000</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>53296000</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="D39" s="3" t="n">
         <v>48231000</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="E39" s="3" t="n">
         <v>45823000</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="F39" s="3" t="n">
         <v>39299000</v>
       </c>
-      <c r="F39" s="3" t="n">
-        <v>35176000</v>
-      </c>
       <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2748,21 +3276,22 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
+        <v>-114000</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>-149000</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>-3219000</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>-1315000</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="F40" s="3" t="n">
         <v>-182000</v>
       </c>
-      <c r="F40" s="3" t="n">
-        <v>-25000</v>
-      </c>
       <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2771,21 +3300,22 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
+        <v>25656000</v>
+      </c>
+      <c r="C41" s="3" t="n">
         <v>25820000</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="D41" s="3" t="n">
         <v>21265000</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="E41" s="3" t="n">
         <v>20612000</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="F41" s="3" t="n">
         <v>17810000</v>
       </c>
-      <c r="F41" s="3" t="n">
-        <v>16737000</v>
-      </c>
       <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2794,21 +3324,22 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
+        <v>31251000</v>
+      </c>
+      <c r="C42" s="3" t="n">
         <v>27625000</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="D42" s="3" t="n">
         <v>30185000</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="E42" s="3" t="n">
         <v>26526000</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="F42" s="3" t="n">
         <v>21671000</v>
       </c>
-      <c r="F42" s="3" t="n">
-        <v>18464000</v>
-      </c>
       <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2817,21 +3348,22 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
+        <v>6347000</v>
+      </c>
+      <c r="C43" s="3" t="n">
         <v>6904000</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="D43" s="3" t="n">
         <v>9871000</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="E43" s="3" t="n">
         <v>8135000</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="F43" s="3" t="n">
         <v>5357000</v>
       </c>
-      <c r="F43" s="3" t="n">
-        <v>3651000</v>
-      </c>
       <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2840,21 +3372,22 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
+        <v>24904000</v>
+      </c>
+      <c r="C44" s="3" t="n">
         <v>20721000</v>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="D44" s="3" t="n">
         <v>20314000</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="E44" s="3" t="n">
         <v>18391000</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="F44" s="3" t="n">
         <v>16314000</v>
       </c>
-      <c r="F44" s="3" t="n">
-        <v>14813000</v>
-      </c>
       <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2863,21 +3396,22 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
+        <v>24904000</v>
+      </c>
+      <c r="C45" s="3" t="n">
         <v>20721000</v>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="D45" s="3" t="n">
         <v>20314000</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="E45" s="3" t="n">
         <v>18391000</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="F45" s="3" t="n">
         <v>16314000</v>
       </c>
-      <c r="F45" s="3" t="n">
-        <v>14813000</v>
-      </c>
       <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2886,21 +3420,22 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
+        <v>43916000</v>
+      </c>
+      <c r="C46" s="3" t="n">
         <v>41944000</v>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="D46" s="3" t="n">
         <v>33263000</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="E46" s="3" t="n">
         <v>31162000</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="F46" s="3" t="n">
         <v>30544000</v>
       </c>
-      <c r="F46" s="3" t="n">
-        <v>28729000</v>
-      </c>
       <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2909,21 +3444,22 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
+        <v>107228000</v>
+      </c>
+      <c r="C47" s="3" t="n">
         <v>92330000</v>
       </c>
-      <c r="C47" s="3" t="n">
+      <c r="D47" s="3" t="n">
         <v>85367000</v>
       </c>
-      <c r="D47" s="3" t="n">
+      <c r="E47" s="3" t="n">
         <v>71790000</v>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="F47" s="3" t="n">
         <v>69315000</v>
       </c>
-      <c r="F47" s="3" t="n">
-        <v>71542000</v>
-      </c>
       <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2932,21 +3468,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
+        <v>151144000</v>
+      </c>
+      <c r="C48" s="3" t="n">
         <v>134274000</v>
       </c>
-      <c r="C48" s="3" t="n">
+      <c r="D48" s="3" t="n">
         <v>118630000</v>
       </c>
-      <c r="D48" s="3" t="n">
+      <c r="E48" s="3" t="n">
         <v>102952000</v>
       </c>
-      <c r="E48" s="3" t="n">
+      <c r="F48" s="3" t="n">
         <v>99859000</v>
       </c>
-      <c r="F48" s="3" t="n">
-        <v>100271000</v>
-      </c>
       <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2955,28 +3492,29 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
+        <v>150804000</v>
+      </c>
+      <c r="C49" s="3" t="n">
         <v>135199000</v>
       </c>
-      <c r="C49" s="3" t="n">
+      <c r="D49" s="3" t="n">
         <v>118279000</v>
       </c>
-      <c r="D49" s="3" t="n">
+      <c r="E49" s="3" t="n">
         <v>102750000</v>
       </c>
-      <c r="E49" s="3" t="n">
+      <c r="F49" s="3" t="n">
         <v>99487000</v>
       </c>
-      <c r="F49" s="3" t="n">
-        <v>102136000</v>
-      </c>
       <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4444,7 +4982,1755 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H73"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ordinary Shares Number</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>78971000</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>74998000</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>68065000</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>61890000</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>53212000</v>
+      </c>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Share Issued</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>78971000</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>74998000</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>68065000</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>61890000</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>53212000</v>
+      </c>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Net Debt</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="3" t="n">
+        <v>55183000</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>123527000</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>129200000</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>113011000</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>82346000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Total Debt</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>280422000</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>248082000</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>235163000</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>211221000</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>190301000</v>
+      </c>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Tangible Book Value</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>1097467000</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>725470000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>550641000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>416544000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>300565000</v>
+      </c>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Invested Capital</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>1312459000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>931085000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>751229000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>613207000</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>489357000</v>
+      </c>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>733149000</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>418444000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>326170000</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>241495000</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>167835000</v>
+      </c>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Net Tangible Assets</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>1097467000</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>725470000</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>550641000</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>416544000</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>300565000</v>
+      </c>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Capital Lease Obligations</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>73915000</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>50915000</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>43019000</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>22995000</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>9957000</v>
+      </c>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Common Stock Equity</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>1105952000</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>733918000</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>559085000</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>424981000</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>309013000</v>
+      </c>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Total Capitalization</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>1235468000</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>863747000</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>689205000</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>558917000</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>445053000</v>
+      </c>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Total Equity Gross Minority Interest</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>1105952000</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>733918000</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>559085000</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>424981000</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>309013000</v>
+      </c>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Stockholders Equity</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>1105952000</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>733918000</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>559085000</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>424981000</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>309013000</v>
+      </c>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Gains Losses Not Affecting Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>-207000</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>-617000</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>1088000</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>1113000</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>-2755000</v>
+      </c>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Other Equity Adjustments</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>-207000</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>-617000</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>1088000</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>1113000</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>-2755000</v>
+      </c>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>-504359000</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>-490078000</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>-488057000</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>-470121000</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>-461023000</v>
+      </c>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Additional Paid In Capital</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>1610439000</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>1224538000</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>1045986000</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>893927000</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>772738000</v>
+      </c>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Capital Stock</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>79000</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>75000</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>68000</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>62000</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>53000</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>79000</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>75000</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>68000</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>62000</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>53000</v>
+      </c>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Preferred Stock</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Total Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>459927000</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>434505000</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>419443000</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>371869000</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>335655000</v>
+      </c>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Total Non Current Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>200499000</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>177222000</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>170301000</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>155026000</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>144648000</v>
+      </c>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Long Term Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>200499000</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>177222000</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>170301000</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>155026000</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>144648000</v>
+      </c>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Long Term Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>70983000</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>47393000</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>40181000</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>21090000</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>8608000</v>
+      </c>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Long Term Debt</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>129516000</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>129829000</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>130120000</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>133936000</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>136040000</v>
+      </c>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>259428000</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>257283000</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>249142000</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>216843000</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>191007000</v>
+      </c>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>342000</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>288000</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>255000</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>256000</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>185000</v>
+      </c>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n"/>
+      <c r="C29" s="3" t="n"/>
+      <c r="D29" s="3" t="n"/>
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" s="3" t="n"/>
+      <c r="G29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>1439000</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Current Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>79923000</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>70860000</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>64862000</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>56195000</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>45653000</v>
+      </c>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Current Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>2932000</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>3522000</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>2838000</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>1905000</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>1349000</v>
+      </c>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Current Debt</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>76991000</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>67338000</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>62024000</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>54290000</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>44304000</v>
+      </c>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Other Current Borrowings</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>41225000</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>33975000</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>27978000</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>22183000</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>20312000</v>
+      </c>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Current Notes Payable</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>35766000</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>33363000</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>34046000</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>32107000</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>23992000</v>
+      </c>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Pensionand Other Post Retirement Benefit Plans Current</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>4017000</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>5506000</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>5609000</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>3853000</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>4387000</v>
+      </c>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Payables And Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>175146000</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>180629000</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>178416000</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>156539000</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>140782000</v>
+      </c>
+      <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Current Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>24741000</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>35732000</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>26820000</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>22132000</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>14998000</v>
+      </c>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Interest Payable</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>745000</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>1599000</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>740000</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>1802000</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>996000</v>
+      </c>
+      <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>150405000</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>144897000</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>151596000</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>134407000</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>125784000</v>
+      </c>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Total Tax Payable</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>2245000</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>965000</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>1451000</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>1445000</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>918000</v>
+      </c>
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>148160000</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>143932000</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>150145000</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>132962000</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>124866000</v>
+      </c>
+      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>1565879000</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>1168423000</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>978528000</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>796850000</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>644668000</v>
+      </c>
+      <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Total Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>573302000</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>492696000</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>403216000</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>338512000</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>285826000</v>
+      </c>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Other Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>67183000</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>58501000</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>42421000</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>38583000</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>26709000</v>
+      </c>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Assets</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>6682000</v>
+      </c>
+      <c r="C45" s="3" t="n"/>
+      <c r="D45" s="3" t="n"/>
+      <c r="E45" s="3" t="n"/>
+      <c r="F45" s="3" t="n"/>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Assets</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>6682000</v>
+      </c>
+      <c r="C46" s="3" t="n"/>
+      <c r="D46" s="3" t="n"/>
+      <c r="E46" s="3" t="n"/>
+      <c r="F46" s="3" t="n"/>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Goodwill And Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>8485000</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>8448000</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>8444000</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>8437000</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>8448000</v>
+      </c>
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>8485000</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>8448000</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>8444000</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>8437000</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>8448000</v>
+      </c>
+      <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Net PPE</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>490952000</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>425747000</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>352351000</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>291492000</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>250669000</v>
+      </c>
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>-241018000</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>-232913000</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>-227918000</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>-223897000</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>-209085000</v>
+      </c>
+      <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Gross PPE</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>731970000</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>658660000</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>580269000</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>515389000</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>459754000</v>
+      </c>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Construction In Progress</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>51487000</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>39808000</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>14929000</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>11075000</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>11839000</v>
+      </c>
+      <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Other Properties</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>71949000</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>49697000</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>42048000</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>22106000</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>9216000</v>
+      </c>
+      <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Machinery Furniture Equipment</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>465933000</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>429085000</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>387036000</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>351530000</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>316704000</v>
+      </c>
+      <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Buildings And Improvements</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>140694000</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>138163000</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>134349000</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>128771000</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>120088000</v>
+      </c>
+      <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Land And Improvements</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>1907000</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>1907000</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>1907000</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>1907000</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>1907000</v>
+      </c>
+      <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>992577000</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>675727000</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>575312000</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>458338000</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>358842000</v>
+      </c>
+      <c r="G58" s="3" t="n"/>
+      <c r="H58" s="3" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Other Current Assets</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>37958000</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>32183000</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>30353000</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>20824000</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>18617000</v>
+      </c>
+      <c r="G59" s="3" t="n"/>
+      <c r="H59" s="3" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Restricted Cash</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>9672000</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>9895000</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>13756000</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>22496000</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>15667000</v>
+      </c>
+      <c r="G60" s="3" t="n"/>
+      <c r="H60" s="3" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Prepaid Assets</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n"/>
+      <c r="C61" s="3" t="n"/>
+      <c r="D61" s="3" t="n"/>
+      <c r="E61" s="3" t="n"/>
+      <c r="F61" s="3" t="n"/>
+      <c r="G61" s="3" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H61" s="3" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>206246000</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>183105000</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>170214000</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>138867000</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>102313000</v>
+      </c>
+      <c r="G62" s="3" t="n"/>
+      <c r="H62" s="3" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Inventories Adjustments Allowances</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>-19463000</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>-16995000</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>-15727000</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>-18381000</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>-16596000</v>
+      </c>
+      <c r="G63" s="3" t="n"/>
+      <c r="H63" s="3" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Finished Goods</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>6555000</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>18822000</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>18927000</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>14701000</v>
+      </c>
+      <c r="G64" s="3" t="n"/>
+      <c r="H64" s="3" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Work In Process</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>120482000</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>95538000</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>77214000</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>61205000</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>45921000</v>
+      </c>
+      <c r="G65" s="3" t="n"/>
+      <c r="H65" s="3" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Raw Materials</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>98672000</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>85740000</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>108606000</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>77116000</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>58287000</v>
+      </c>
+      <c r="G66" s="3" t="n"/>
+      <c r="H66" s="3" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>298996000</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>244404000</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>224028000</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>211452000</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>171101000</v>
+      </c>
+      <c r="G67" s="3" t="n"/>
+      <c r="H67" s="3" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Notes Receivable</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n"/>
+      <c r="C68" s="3" t="n"/>
+      <c r="D68" s="3" t="n"/>
+      <c r="E68" s="3" t="n"/>
+      <c r="F68" s="3" t="n"/>
+      <c r="G68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" s="3" t="n">
+        <v>47000</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v>298996000</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>244404000</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>224028000</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>211452000</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>171101000</v>
+      </c>
+      <c r="G69" s="3" t="n"/>
+      <c r="H69" s="3" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Allowance For Doubtful Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n"/>
+      <c r="C70" s="3" t="n"/>
+      <c r="D70" s="3" t="n"/>
+      <c r="E70" s="3" t="n"/>
+      <c r="F70" s="3" t="n"/>
+      <c r="G70" s="3" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="H70" s="3" t="n">
+        <v>-1805000</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Gross Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n"/>
+      <c r="C71" s="3" t="n"/>
+      <c r="D71" s="3" t="n"/>
+      <c r="E71" s="3" t="n"/>
+      <c r="F71" s="3" t="n"/>
+      <c r="G71" s="3" t="n">
+        <v>116802000</v>
+      </c>
+      <c r="H71" s="3" t="n">
+        <v>76959000</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Cash Cash Equivalents And Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v>439705000</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>206140000</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>136961000</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>64699000</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>51144000</v>
+      </c>
+      <c r="G72" s="3" t="n"/>
+      <c r="H72" s="3" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Cash And Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v>439705000</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>206140000</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>136961000</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>64699000</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>51144000</v>
+      </c>
+      <c r="G73" s="3" t="n"/>
+      <c r="H73" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5668,13 +7954,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5684,6 +7970,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5694,30 +7981,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-06-30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-03-31</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2024-12-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-09-30</t>
         </is>
@@ -5730,21 +8022,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>-143696000</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>-104721000</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>-78832000</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>-91033000</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>-79369000</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>-53127000</v>
-      </c>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5753,21 +8046,22 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>-43025000</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>-38039000</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>-55501000</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>-39208000</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="F3" s="3" t="n">
         <v>-30376000</v>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>-29167000</v>
-      </c>
       <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5776,21 +8070,22 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>51579000</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>42652000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>62325000</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>47217000</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="3" t="n">
         <v>30411000</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>32358000</v>
-      </c>
       <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5799,21 +8094,22 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>382448000</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>176353000</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>146791000</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>124105000</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="F5" s="3" t="n">
         <v>71665000</v>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>87799000</v>
-      </c>
       <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5822,21 +8118,22 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>-58343000</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>-75144000</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>-50370000</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>-25559000</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F6" s="3" t="n">
         <v>-28454000</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>-28511000</v>
-      </c>
       <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5845,21 +8142,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>1815000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>96000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>2113000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>165000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>109000</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>2305000</v>
-      </c>
       <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5867,16 +8165,17 @@
           <t>Income Tax Paid Supplemental Data</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" s="3" t="n"/>
+      <c r="C8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C8" s="3" t="n"/>
       <c r="D8" s="3" t="n"/>
       <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="n">
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="3" t="n">
         <v>-1000</v>
       </c>
-      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5885,21 +8184,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>449377000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>216035000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>150717000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>87195000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>66811000</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>79133000</v>
-      </c>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5908,21 +8208,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>216035000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>150717000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>87195000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>66811000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>79133000</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>41367000</v>
-      </c>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5931,21 +8232,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>-2483000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>134000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>-9793000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>-1228000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>4880000</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>1941000</v>
-      </c>
       <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5954,21 +8256,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>235825000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>65184000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>73315000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>21612000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>-17202000</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>35825000</v>
-      </c>
       <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5977,21 +8280,22 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>389265000</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>179693000</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>152255000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>125979000</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>70014000</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>89711000</v>
-      </c>
       <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6000,21 +8304,22 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>389265000</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>179693000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>152255000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>125979000</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>70014000</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>89711000</v>
-      </c>
       <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6023,21 +8328,22 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>-1737000</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>-1273000</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>-1360000</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>-6135000</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="F15" s="3" t="n">
         <v>-1686000</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>-1279000</v>
-      </c>
       <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6049,10 +8355,11 @@
       <c r="C16" s="3" t="n"/>
       <c r="D16" s="3" t="n"/>
       <c r="E16" s="3" t="n"/>
-      <c r="F16" s="3" t="n">
+      <c r="F16" s="3" t="n"/>
+      <c r="G16" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6061,21 +8368,22 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
+        <v>382448000</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>176353000</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="D17" s="3" t="n">
         <v>146791000</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>124105000</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="F17" s="3" t="n">
         <v>71665000</v>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>87799000</v>
-      </c>
       <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6084,21 +8392,22 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
+        <v>382448000</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>176353000</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>146791000</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>124105000</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="F18" s="3" t="n">
         <v>71665000</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>87799000</v>
-      </c>
       <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6107,21 +8416,22 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
+        <v>8554000</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>4613000</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="D19" s="3" t="n">
         <v>6824000</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>8009000</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>35000</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>3191000</v>
-      </c>
       <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -6130,21 +8440,22 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
+        <v>8570000</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>-1027000</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>6302000</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>8010000</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>90000</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>3699000</v>
-      </c>
       <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6153,21 +8464,22 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
+        <v>-43009000</v>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>-33806000</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="D21" s="3" t="n">
         <v>-4698000</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>-39207000</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="F21" s="3" t="n">
         <v>-30321000</v>
       </c>
-      <c r="F21" s="3" t="n">
-        <v>20017000</v>
-      </c>
       <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6176,21 +8488,22 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>51579000</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>32779000</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>11000000</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>47217000</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>30411000</v>
       </c>
-      <c r="F22" s="3" t="n">
-        <v>-16318000</v>
-      </c>
       <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -6199,21 +8512,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>-16000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>5640000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>522000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>-1000</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>-55000</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>-508000</v>
-      </c>
       <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6222,21 +8536,22 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>-16000</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>-4233000</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>-50803000</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>-1000</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="F24" s="3" t="n">
         <v>-55000</v>
       </c>
-      <c r="F24" s="3" t="n">
-        <v>-49184000</v>
-      </c>
       <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6244,14 +8559,15 @@
           <t>Long Term Debt Issuance</t>
         </is>
       </c>
-      <c r="B25" s="3" t="n">
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="3" t="n">
         <v>9873000</v>
       </c>
-      <c r="C25" s="3" t="n"/>
       <c r="D25" s="3" t="n"/>
       <c r="E25" s="3" t="n"/>
       <c r="F25" s="3" t="n"/>
       <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -6260,21 +8576,22 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
+        <v>-68087000</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>-84932000</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>-50478000</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>-38893000</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="F26" s="3" t="n">
         <v>-36301000</v>
       </c>
-      <c r="F26" s="3" t="n">
-        <v>-29270000</v>
-      </c>
       <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6283,21 +8600,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
+        <v>-68087000</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>-84932000</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>-50478000</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="E27" s="3" t="n">
         <v>-38893000</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="F27" s="3" t="n">
         <v>-36301000</v>
       </c>
-      <c r="F27" s="3" t="n">
-        <v>-29270000</v>
-      </c>
       <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6306,21 +8624,22 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
+        <v>-9744000</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>-9793000</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="D28" s="3" t="n">
         <v>-108000</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="E28" s="3" t="n">
         <v>-13334000</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="F28" s="3" t="n">
         <v>-7847000</v>
       </c>
-      <c r="F28" s="3" t="n">
-        <v>-759000</v>
-      </c>
       <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6329,21 +8648,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>-118000</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>-109000</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>-125000</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>-80000</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>-65000</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>-132000</v>
-      </c>
       <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6352,21 +8672,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
+        <v>-118000</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>-109000</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="D30" s="3" t="n">
         <v>-125000</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="E30" s="3" t="n">
         <v>-80000</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="F30" s="3" t="n">
         <v>-65000</v>
       </c>
-      <c r="F30" s="3" t="n">
-        <v>-132000</v>
-      </c>
       <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6375,21 +8696,22 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
+        <v>-58225000</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>-75030000</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="D31" s="3" t="n">
         <v>-50245000</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>-25479000</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="F31" s="3" t="n">
         <v>-28389000</v>
       </c>
-      <c r="F31" s="3" t="n">
-        <v>-28379000</v>
-      </c>
       <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6401,10 +8723,11 @@
       <c r="C32" s="3" t="n"/>
       <c r="D32" s="3" t="n"/>
       <c r="E32" s="3" t="n"/>
-      <c r="F32" s="3" t="n">
+      <c r="F32" s="3" t="n"/>
+      <c r="G32" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G32" s="3" t="n">
+      <c r="H32" s="3" t="n">
         <v>2000</v>
       </c>
     </row>
@@ -6415,21 +8738,22 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
+        <v>-58225000</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>-75035000</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="D33" s="3" t="n">
         <v>-50245000</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="E33" s="3" t="n">
         <v>-25479000</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="F33" s="3" t="n">
         <v>-28389000</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>-28379000</v>
-      </c>
       <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6438,21 +8762,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
+        <v>-85353000</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>-29577000</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="D34" s="3" t="n">
         <v>-28462000</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="E34" s="3" t="n">
         <v>-65474000</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="F34" s="3" t="n">
         <v>-50915000</v>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>-24616000</v>
-      </c>
       <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -6461,21 +8786,22 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
+        <v>-85353000</v>
+      </c>
+      <c r="C35" s="3" t="n">
         <v>-29577000</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="D35" s="3" t="n">
         <v>-28462000</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="E35" s="3" t="n">
         <v>-65474000</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="F35" s="3" t="n">
         <v>-50915000</v>
       </c>
-      <c r="F35" s="3" t="n">
-        <v>-24616000</v>
-      </c>
       <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -6484,21 +8810,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>-90123000</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>-33743000</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>-28175000</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>-62079000</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>-51948000</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>-25642000</v>
-      </c>
       <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6510,10 +8837,11 @@
       <c r="C37" s="3" t="n"/>
       <c r="D37" s="3" t="n"/>
       <c r="E37" s="3" t="n"/>
-      <c r="F37" s="3" t="n">
+      <c r="F37" s="3" t="n"/>
+      <c r="G37" s="3" t="n">
         <v>-1439000</v>
       </c>
-      <c r="G37" s="3" t="n">
+      <c r="H37" s="3" t="n">
         <v>-131000</v>
       </c>
     </row>
@@ -6524,21 +8852,22 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
+        <v>23832000</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>9333000</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>20763000</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>11568000</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="F38" s="3" t="n">
         <v>-339000</v>
       </c>
-      <c r="F38" s="3" t="n">
-        <v>5869000</v>
-      </c>
       <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6547,21 +8876,22 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
+        <v>-29251000</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>-11232000</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="D39" s="3" t="n">
         <v>-30517000</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="E39" s="3" t="n">
         <v>-13234000</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="F39" s="3" t="n">
         <v>558000</v>
       </c>
-      <c r="F39" s="3" t="n">
-        <v>-15814000</v>
-      </c>
       <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6570,21 +8900,22 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
+        <v>-4931000</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>4631000</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>27723000</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>14793000</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="F40" s="3" t="n">
         <v>18327000</v>
       </c>
-      <c r="F40" s="3" t="n">
-        <v>52192000</v>
-      </c>
       <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6593,21 +8924,22 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
+        <v>-9159000</v>
+      </c>
+      <c r="C41" s="3" t="n">
         <v>10844000</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="D41" s="3" t="n">
         <v>10540000</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="E41" s="3" t="n">
         <v>6696000</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="F41" s="3" t="n">
         <v>-1569000</v>
       </c>
-      <c r="F41" s="3" t="n">
-        <v>3214000</v>
-      </c>
       <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6616,21 +8948,22 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
+        <v>4228000</v>
+      </c>
+      <c r="C42" s="3" t="n">
         <v>-6213000</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="D42" s="3" t="n">
         <v>17183000</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="E42" s="3" t="n">
         <v>8097000</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="F42" s="3" t="n">
         <v>19896000</v>
       </c>
-      <c r="F42" s="3" t="n">
-        <v>48978000</v>
-      </c>
       <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6639,21 +8972,22 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
+        <v>4228000</v>
+      </c>
+      <c r="C43" s="3" t="n">
         <v>-6213000</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="D43" s="3" t="n">
         <v>17183000</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="E43" s="3" t="n">
         <v>8097000</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="F43" s="3" t="n">
         <v>19896000</v>
       </c>
-      <c r="F43" s="3" t="n">
-        <v>48977000</v>
-      </c>
       <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6665,10 +8999,11 @@
       <c r="C44" s="3" t="n"/>
       <c r="D44" s="3" t="n"/>
       <c r="E44" s="3" t="n"/>
-      <c r="F44" s="3" t="n">
+      <c r="F44" s="3" t="n"/>
+      <c r="G44" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="G44" s="3" t="n">
+      <c r="H44" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6682,10 +9017,11 @@
       <c r="C45" s="3" t="n"/>
       <c r="D45" s="3" t="n"/>
       <c r="E45" s="3" t="n"/>
-      <c r="F45" s="3" t="n">
+      <c r="F45" s="3" t="n"/>
+      <c r="G45" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="G45" s="3" t="n">
+      <c r="H45" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6699,12 +9035,13 @@
       <c r="C46" s="3" t="n"/>
       <c r="D46" s="3" t="n"/>
       <c r="E46" s="3" t="n"/>
-      <c r="F46" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="F46" s="3" t="n"/>
       <c r="G46" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="H46" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6713,21 +9050,22 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
+        <v>-25329000</v>
+      </c>
+      <c r="C47" s="3" t="n">
         <v>-16110000</v>
       </c>
-      <c r="C47" s="3" t="n">
+      <c r="D47" s="3" t="n">
         <v>-33564000</v>
       </c>
-      <c r="D47" s="3" t="n">
+      <c r="E47" s="3" t="n">
         <v>-34854000</v>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="F47" s="3" t="n">
         <v>-16194000</v>
       </c>
-      <c r="F47" s="3" t="n">
-        <v>-26652000</v>
-      </c>
       <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6736,21 +9074,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
+        <v>-54444000</v>
+      </c>
+      <c r="C48" s="3" t="n">
         <v>-20365000</v>
       </c>
-      <c r="C48" s="3" t="n">
+      <c r="D48" s="3" t="n">
         <v>-12580000</v>
       </c>
-      <c r="D48" s="3" t="n">
+      <c r="E48" s="3" t="n">
         <v>-40352000</v>
       </c>
-      <c r="E48" s="3" t="n">
+      <c r="F48" s="3" t="n">
         <v>-54300000</v>
       </c>
-      <c r="F48" s="3" t="n">
-        <v>-39798000</v>
-      </c>
       <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6759,21 +9098,22 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
+        <v>-54444000</v>
+      </c>
+      <c r="C49" s="3" t="n">
         <v>-20365000</v>
       </c>
-      <c r="C49" s="3" t="n">
+      <c r="D49" s="3" t="n">
         <v>-12580000</v>
       </c>
-      <c r="D49" s="3" t="n">
+      <c r="E49" s="3" t="n">
         <v>-40352000</v>
       </c>
-      <c r="E49" s="3" t="n">
+      <c r="F49" s="3" t="n">
         <v>-54300000</v>
       </c>
-      <c r="F49" s="3" t="n">
-        <v>-39843000</v>
-      </c>
       <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6782,21 +9122,22 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
+        <v>2178000</v>
+      </c>
+      <c r="C50" s="3" t="n">
         <v>-5634000</v>
       </c>
-      <c r="C50" s="3" t="n">
+      <c r="D50" s="3" t="n">
         <v>1389000</v>
       </c>
-      <c r="D50" s="3" t="n">
+      <c r="E50" s="3" t="n">
         <v>1055000</v>
       </c>
-      <c r="E50" s="3" t="n">
+      <c r="F50" s="3" t="n">
         <v>2168000</v>
       </c>
-      <c r="F50" s="3" t="n">
-        <v>-1993000</v>
-      </c>
       <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6805,21 +9146,22 @@
         </is>
       </c>
       <c r="B51" s="3" t="n">
+        <v>4391000</v>
+      </c>
+      <c r="C51" s="3" t="n">
         <v>2868000</v>
       </c>
-      <c r="C51" s="3" t="n">
+      <c r="D51" s="3" t="n">
         <v>3116000</v>
       </c>
-      <c r="D51" s="3" t="n">
+      <c r="E51" s="3" t="n">
         <v>3164000</v>
       </c>
-      <c r="E51" s="3" t="n">
+      <c r="F51" s="3" t="n">
         <v>2562000</v>
       </c>
-      <c r="F51" s="3" t="n">
-        <v>2949000</v>
-      </c>
       <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -6828,21 +9170,22 @@
         </is>
       </c>
       <c r="B52" s="3" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C52" s="3" t="n">
         <v>7798000</v>
       </c>
-      <c r="C52" s="3" t="n">
+      <c r="D52" s="3" t="n">
         <v>4000</v>
       </c>
-      <c r="D52" s="3" t="n">
+      <c r="E52" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="E52" s="3" t="n">
+      <c r="F52" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F52" s="3" t="n">
-        <v>1630000</v>
-      </c>
       <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -6850,153 +9193,200 @@
           <t>Amortization Of Securities</t>
         </is>
       </c>
-      <c r="B53" s="3" t="n"/>
+      <c r="B53" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="C53" s="3" t="n"/>
       <c r="D53" s="3" t="n"/>
-      <c r="E53" s="3" t="n">
+      <c r="E53" s="3" t="n"/>
+      <c r="F53" s="3" t="n">
         <v>-508000</v>
       </c>
-      <c r="F53" s="3" t="n"/>
       <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Depreciation Amortization Depletion</t>
+          <t>Deferred Tax</t>
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>8205000</v>
-      </c>
-      <c r="C54" s="3" t="n">
-        <v>7366000</v>
-      </c>
-      <c r="D54" s="3" t="n">
-        <v>6400000</v>
-      </c>
-      <c r="E54" s="3" t="n">
-        <v>5725000</v>
-      </c>
+        <v>1049000</v>
+      </c>
+      <c r="C54" s="3" t="n"/>
+      <c r="D54" s="3" t="n"/>
+      <c r="E54" s="3" t="n"/>
       <c r="F54" s="3" t="n">
-        <v>5356000</v>
+        <v>0</v>
       </c>
       <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Depreciation And Amortization</t>
+          <t>Deferred Income Tax</t>
         </is>
       </c>
       <c r="B55" s="3" t="n">
-        <v>8205000</v>
-      </c>
-      <c r="C55" s="3" t="n">
-        <v>7366000</v>
-      </c>
-      <c r="D55" s="3" t="n">
-        <v>6400000</v>
-      </c>
-      <c r="E55" s="3" t="n">
-        <v>5725000</v>
-      </c>
+        <v>1049000</v>
+      </c>
+      <c r="C55" s="3" t="n"/>
+      <c r="D55" s="3" t="n"/>
+      <c r="E55" s="3" t="n"/>
       <c r="F55" s="3" t="n">
-        <v>5356000</v>
+        <v>0</v>
       </c>
       <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Operating Gains Losses</t>
+          <t>Depreciation Amortization Depletion</t>
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>526000</v>
+        <v>9229000</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>5774000</v>
+        <v>8205000</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>-5425000</v>
+        <v>7366000</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>258000</v>
+        <v>6400000</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>112775000</v>
+        <v>5725000</v>
       </c>
       <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Gain Loss On Investment Securities</t>
+          <t>Depreciation And Amortization</t>
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>732000</v>
+        <v>9229000</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>38000</v>
-      </c>
-      <c r="D57" s="3" t="n"/>
-      <c r="E57" s="3" t="n"/>
-      <c r="F57" s="3" t="n"/>
+        <v>8205000</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>7366000</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>6400000</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>5725000</v>
+      </c>
       <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Net Foreign Currency Exchange Gain Loss</t>
+          <t>Operating Gains Losses</t>
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>-213000</v>
+        <v>2196000</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>5714000</v>
+        <v>526000</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>-5479000</v>
+        <v>5774000</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>250000</v>
+        <v>-5425000</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>714000</v>
+        <v>258000</v>
       </c>
       <c r="G58" s="3" t="n"/>
+      <c r="H58" s="3" t="n"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>Gain Loss On Investment Securities</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>963000</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>732000</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>38000</v>
+      </c>
+      <c r="E59" s="3" t="n"/>
+      <c r="F59" s="3" t="n"/>
+      <c r="G59" s="3" t="n"/>
+      <c r="H59" s="3" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Net Foreign Currency Exchange Gain Loss</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>1217000</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>-213000</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>5714000</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>-5479000</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>250000</v>
+      </c>
+      <c r="G60" s="3" t="n"/>
+      <c r="H60" s="3" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
           <t>Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B59" s="3" t="n">
+      <c r="B61" s="3" t="n">
+        <v>-14281000</v>
+      </c>
+      <c r="C61" s="3" t="n">
         <v>-2022000</v>
       </c>
-      <c r="C59" s="3" t="n">
+      <c r="D61" s="3" t="n">
         <v>-17936000</v>
       </c>
-      <c r="D59" s="3" t="n">
+      <c r="E61" s="3" t="n">
         <v>-9098000</v>
       </c>
-      <c r="E59" s="3" t="n">
+      <c r="F61" s="3" t="n">
         <v>-9172000</v>
       </c>
-      <c r="F59" s="3" t="n">
-        <v>-119691000</v>
-      </c>
-      <c r="G59" s="3" t="n"/>
+      <c r="G61" s="3" t="n"/>
+      <c r="H61" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
